--- a/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AA9249-79F6-438E-BFEA-8BD6C1051F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B4D8C8-FF43-442A-9F9A-7126B3F09967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,77 +59,171 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1번 문제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1번 보기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2번 보기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3번 보기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2번 문제</t>
-  </si>
-  <si>
-    <t>3번 문제</t>
-  </si>
-  <si>
-    <t>4번 문제</t>
-  </si>
-  <si>
-    <t>5번 문제</t>
-  </si>
-  <si>
-    <t>6번 문제</t>
-  </si>
-  <si>
-    <t>7번 문제</t>
-  </si>
-  <si>
-    <t>8번 문제</t>
-  </si>
-  <si>
-    <t>9번 문제</t>
-  </si>
-  <si>
-    <t>10번 문제</t>
-  </si>
-  <si>
-    <t>11번 문제</t>
-  </si>
-  <si>
-    <t>12번 문제</t>
-  </si>
-  <si>
-    <t>13번 문제</t>
-  </si>
-  <si>
-    <t>14번 문제</t>
-  </si>
-  <si>
-    <t>15번 문제</t>
-  </si>
-  <si>
-    <t>16번 문제</t>
-  </si>
-  <si>
-    <t>17번 문제</t>
-  </si>
-  <si>
-    <t>18번 문제</t>
-  </si>
-  <si>
-    <t>19번 문제</t>
-  </si>
-  <si>
-    <t>20번 문제</t>
+    <t>연모아 3주년은 재미있었나요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스플래툰 3 전야제 페스 승리 팀은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스플래툰 3 그랜드 페스 승리 팀은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미래</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네!!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스플</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연모아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불꽃탄이 추가된 페스티벌은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연모아 2주년 로무가 제작한 게임의 이름은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수초생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스초생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14차
+밴드에서 담당하고 싶은 악기는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12차
+쉬는 날에는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17차
+하루 종일 통째로 빌릴 수 있다면?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0번째 카드의 주인공은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X매치가 추가된 시즌은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022년 여름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022년 겨울</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022년 가을</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가슬이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하넬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수치생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새먼런에 가장 마지막에 추가된 스테이지는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연어 심장 투기장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사계절 훈제 공방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연어알젓 교차로 옛터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스플래툰 3에서 가장 처음 공개된 쿠마 무기는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠마 롤러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠마 스트링거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠마 와이퍼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2 + 2 x 2 의 답은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연모아 매니저인 사람은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -216,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -247,6 +341,9 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,11 +653,11 @@
   <dimension ref="A1:F303"/>
   <sheetFormatPr defaultColWidth="17.625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.875" style="4" customWidth="1"/>
-    <col min="2" max="3" width="18.875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="19" style="6" customWidth="1"/>
-    <col min="5" max="5" width="19" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="47.5" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.5" style="6" customWidth="1"/>
+    <col min="5" max="6" width="35.5" style="2" customWidth="1"/>
     <col min="7" max="16384" width="17.625" style="2"/>
   </cols>
   <sheetData>
@@ -589,19 +686,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -609,19 +706,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -632,16 +729,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -649,19 +746,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -669,40 +766,26 @@
         <v>5</v>
       </c>
       <c r="B6" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
@@ -712,16 +795,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -729,59 +812,45 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:6" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -789,119 +858,84 @@
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>9</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>9</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -912,16 +946,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="6">
+        <v>6</v>
+      </c>
+      <c r="E18" s="7">
         <v>8</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>9</v>
+      <c r="F18" s="5">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -929,19 +963,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>8</v>
+        <v>34</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -952,16 +986,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -969,19 +1003,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1001,8 +1035,6 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
@@ -2396,40 +2428,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E299">
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{85758CF9-4AF1-483A-978B-C6FE5D6837D7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{85758CF9-4AF1-483A-978B-C6FE5D6837D7}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>E2:E299</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B4D8C8-FF43-442A-9F9A-7126B3F09967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F32448-E71A-43C3-A8C8-BFFA8BC31284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스플래툰 3 전야제 페스 승리 팀은?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>가위</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -104,18 +100,6 @@
   </si>
   <si>
     <t>네!!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스플</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기타</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연모아</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -150,18 +134,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0번째 카드의 주인공은?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>로무</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>X매치가 추가된 시즌은?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2022년 여름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,6 +199,150 @@
   </si>
   <si>
     <t>연모아 매니저인 사람은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0번째 카드에 그려져 있는 사람은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026년은 무슨 해?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>병오년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>을사년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑진년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이플</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헬다이버즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스플래툰 3 전야제 페스티벌의 승리 팀은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타게임클립</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연모아에 들어와있는 로무의 계정 수 는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연어알바쉬는시간 탭에 없는 방 이름은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구름이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연홍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>치누</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레몬 1개에는 레몬 몇 개 분량의 비타민 C가 들어있을까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레몬 한 개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레몬 반 개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레몬 두 개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 연모아에 들어와있지 않은 봇은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지구가 태양을 한바퀴 도는 데 걸리는 시간은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스플래툰 3 X매치가 추가된 시즌은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로무가 현재 하고 있는 알바는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맘스터치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>샤브샤브</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼드 마커의 1힛 데미지가 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스플래툰 3 사이드오더에서 파란색 계열 칩의 종류는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서포트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드론</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무브</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -310,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -345,11 +465,85 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -650,18 +844,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F303"/>
+  <dimension ref="A1:K303"/>
   <sheetFormatPr defaultColWidth="17.625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.875" style="4" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="47.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="57.625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.5" style="6" customWidth="1"/>
     <col min="5" max="6" width="35.5" style="2" customWidth="1"/>
     <col min="7" max="16384" width="17.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -680,8 +874,20 @@
       <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H1" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1" s="2">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2">
+        <v>2</v>
+      </c>
+      <c r="K1" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -689,19 +895,35 @@
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2" s="2">
+        <f>COUNTIF($B$2:$B$21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <f>COUNTIF($B$2:$B$21,1)</f>
+        <v>7</v>
+      </c>
+      <c r="J2" s="2">
+        <f>COUNTIF($B$2:$B$21,2)</f>
+        <v>6</v>
+      </c>
+      <c r="K2" s="2">
+        <f>COUNTIF($B$2:$B$21,3)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -709,19 +931,19 @@
         <v>3</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="E3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -729,19 +951,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -749,45 +971,59 @@
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -795,45 +1031,59 @@
         <v>1</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" ht="34.5" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -841,82 +1091,117 @@
         <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="D14" s="6">
+        <v>38</v>
+      </c>
+      <c r="E14" s="7">
+        <v>41</v>
+      </c>
+      <c r="F14" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="5"/>
+        <v>62</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
@@ -926,16 +1211,16 @@
         <v>2</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -946,7 +1231,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D18" s="6">
         <v>6</v>
@@ -966,16 +1251,16 @@
         <v>2</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -986,16 +1271,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="E20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="F20" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1009,13 +1294,13 @@
         <v>6</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2428,6 +2713,20 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F32448-E71A-43C3-A8C8-BFFA8BC31284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E144D3DF-46F2-4536-9864-48F548CDF84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -326,10 +326,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>볼드 마커의 1힛 데미지가 아닌 것은?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스플래툰 3 사이드오더에서 파란색 계열 칩의 종류는?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -343,6 +339,10 @@
   </si>
   <si>
     <t>무브</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼드 마커의 1힛 직격 데미지가 아닌 것은?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -472,35 +472,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -525,21 +497,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1151,13 +1109,13 @@
         <v>2</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D14" s="6">
         <v>38</v>
       </c>
       <c r="E14" s="7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="5">
         <v>45</v>
@@ -1171,16 +1129,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2714,17 +2672,17 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
-      <formula>0</formula>
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
-      <formula>2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>3</formula>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E144D3DF-46F2-4536-9864-48F548CDF84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383FC831-B01F-4834-9850-F418246A97A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="80">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,10 +194,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 2 + 2 x 2 의 답은?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>연모아 매니저인 사람은?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -343,6 +339,22 @@
   </si>
   <si>
     <t>볼드 마커의 1힛 직격 데미지가 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x/(y+z) + y(x+z) + z(x+y) = 4 일때, 틀린 답은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y = 36875131794129999827197811565225474825492979968971970996283137471637224634055579</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>z = 154476802108746166441951315019919837485664325669565431700026634898253202035277999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x = 43736126779286972578612526023713901528165375581616136186214379933784234677720360</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -808,8 +820,9 @@
     <col min="1" max="1" width="8.875" style="4" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="6" customWidth="1"/>
     <col min="3" max="3" width="57.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.5" style="6" customWidth="1"/>
-    <col min="5" max="6" width="35.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="103.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="105" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="101.875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="17.625" style="2"/>
   </cols>
   <sheetData>
@@ -853,7 +866,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>7</v>
@@ -889,7 +902,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
@@ -929,7 +942,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>25</v>
@@ -949,16 +962,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -969,16 +982,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1009,16 +1022,16 @@
         <v>3</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1029,16 +1042,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="34.5" x14ac:dyDescent="0.3">
@@ -1069,16 +1082,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1089,16 +1102,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1109,7 +1122,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" s="6">
         <v>38</v>
@@ -1129,16 +1142,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1149,16 +1162,16 @@
         <v>3</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="F16" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1189,16 +1202,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="6">
-        <v>6</v>
-      </c>
-      <c r="E18" s="7">
-        <v>8</v>
-      </c>
-      <c r="F18" s="5">
-        <v>10</v>
+        <v>76</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1209,7 +1222,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>

--- a/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383FC831-B01F-4834-9850-F418246A97A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA4871F-6AE5-4B97-ADF2-2061A8F65C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>

--- a/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA4871F-6AE5-4B97-ADF2-2061A8F65C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B0011F-A837-4399-BBCF-145B8EBEB11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,19 +342,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>x/(y+z) + y(x+z) + z(x+y) = 4 일때, 틀린 답은?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>y = 36875131794129999827197811565225474825492979968971970996283137471637224634055579</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>z = 154476802108746166441951315019919837485664325669565431700026634898253202035277999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x = 43736126779286972578612526023713901528165375581616136186214379933784234677720360</t>
+    <t>밀레니엄 문제 중 증명이 된 문제는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸앵카레 정리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리만 가설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P-NP 문제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -820,9 +820,9 @@
     <col min="1" max="1" width="8.875" style="4" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="6" customWidth="1"/>
     <col min="3" max="3" width="57.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="103.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="105" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="101.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.75" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="17.625" style="2"/>
   </cols>
   <sheetData>
@@ -887,11 +887,11 @@
       </c>
       <c r="J2" s="2">
         <f>COUNTIF($B$2:$B$21,2)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2" s="2">
         <f>COUNTIF($B$2:$B$21,3)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1019,19 +1019,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1139,16 +1139,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>73</v>
@@ -1162,16 +1162,16 @@
         <v>3</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1205,13 +1205,13 @@
         <v>76</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1314,8 +1314,6 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>

--- a/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/FinalQuizData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B0011F-A837-4399-BBCF-145B8EBEB11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5860A2ED-27BD-47C4-9D5C-ACDF2ADDFF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -258,14 +258,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>연홍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>치누</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>레몬 1개에는 레몬 몇 개 분량의 비타민 C가 들어있을까?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -355,6 +347,14 @@
   </si>
   <si>
     <t>P-NP 문제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카미봇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알로항</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -942,7 +942,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>25</v>
@@ -962,16 +962,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="E6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1022,16 +1022,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1102,16 +1102,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1122,7 +1122,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D14" s="6">
         <v>38</v>
@@ -1142,16 +1142,16 @@
         <v>2</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1162,16 +1162,16 @@
         <v>3</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1202,16 +1202,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
